--- a/data/trans_orig/P13A_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023</t>
+          <t>Población con cefaleas crónicas (15 días o más al mes durante más de 3 meses) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34474</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>44374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>616720</t>
+          <t>616995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628335</t>
+          <t>628706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639696</t>
+          <t>638737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657394</t>
+          <t>657357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262457</t>
+          <t>1262309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1283036</t>
+          <t>1282656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>26490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33923</t>
+          <t>34743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57000</t>
+          <t>58893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38232</t>
+          <t>38944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76506</t>
+          <t>77263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1162753</t>
+          <t>1162844</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1183497</t>
+          <t>1182709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900032</t>
+          <t>898139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923109</t>
+          <t>922289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2069860</t>
+          <t>2069103</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2108134</t>
+          <t>2107422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15368</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>43660</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52589</t>
+          <t>53487</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>687495</t>
+          <t>686190</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>699364</t>
+          <t>699084</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>886125</t>
+          <t>887570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>915862</t>
+          <t>916088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1581555</t>
+          <t>1580657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1609585</t>
+          <t>1609650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31164</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64415</t>
+          <t>63720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37083</t>
+          <t>37218</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68982</t>
+          <t>70901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>912028</t>
+          <t>911267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920935</t>
+          <t>920490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1021500</t>
+          <t>1022195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1054751</t>
+          <t>1053570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1940240</t>
+          <t>1938321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972139</t>
+          <t>1972004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25102</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118711</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173404</t>
+          <t>172756</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152673</t>
+          <t>153163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211370</t>
+          <t>211769</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3396281</t>
+          <t>3396675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3422966</t>
+          <t>3422865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3474944</t>
+          <t>3475592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3529637</t>
+          <t>3532211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6885046</t>
+          <t>6884647</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6943743</t>
+          <t>6943253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P13A_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35433</t>
+          <t>37356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44374</t>
+          <t>48233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>624242</t>
+          <t>678802</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>616995</t>
+          <t>671708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>628706</t>
+          <t>683500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>650301</t>
+          <t>706304</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>638737</t>
+          <t>694162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>657357</t>
+          <t>713399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1274542</t>
+          <t>1385106</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262309</t>
+          <t>1370733</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1282656</t>
+          <t>1394671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>632513</t>
+          <t>687448</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>632513</t>
+          <t>687448</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>632513</t>
+          <t>687448</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674170</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674170</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674170</t>
+          <t>731518</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1306683</t>
+          <t>1418966</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1306683</t>
+          <t>1418966</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1306683</t>
+          <t>1418966</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44141</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34743</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58893</t>
+          <t>63521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58909</t>
+          <t>64003</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38944</t>
+          <t>50957</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77263</t>
+          <t>82466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1174566</t>
+          <t>1029998</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1162844</t>
+          <t>1018106</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1182709</t>
+          <t>1036018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>912891</t>
+          <t>1020606</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>898139</t>
+          <t>1006165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>922289</t>
+          <t>1031466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2087457</t>
+          <t>2050605</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2069103</t>
+          <t>2032142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2107422</t>
+          <t>2063651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1189334</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1189334</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1189334</t>
+          <t>1044921</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957032</t>
+          <t>1069686</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957032</t>
+          <t>1069686</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957032</t>
+          <t>1069686</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2146366</t>
+          <t>2114608</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2146366</t>
+          <t>2114608</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2146366</t>
+          <t>2114608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>26171</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>46134</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24494</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53487</t>
+          <t>59365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>694624</t>
+          <t>790771</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>686190</t>
+          <t>782004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>699084</t>
+          <t>795795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>900205</t>
+          <t>771728</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>887570</t>
+          <t>761562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>916088</t>
+          <t>781525</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1594830</t>
+          <t>1562499</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1580657</t>
+          <t>1549494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1609650</t>
+          <t>1571978</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702914</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>807696</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>807696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931230</t>
+          <t>807696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1634144</t>
+          <t>1608859</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1634144</t>
+          <t>1608859</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1634144</t>
+          <t>1608859</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>34416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63720</t>
+          <t>59495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>50766</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37218</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70901</t>
+          <t>65660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>917243</t>
+          <t>979535</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911267</t>
+          <t>972894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920490</t>
+          <t>982586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1041456</t>
+          <t>1063399</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1022195</t>
+          <t>1048723</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1053570</t>
+          <t>1073802</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1958699</t>
+          <t>2042935</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938321</t>
+          <t>2028041</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1972004</t>
+          <t>2055086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>985483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1085915</t>
+          <t>1108218</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1085915</t>
+          <t>1108218</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1085915</t>
+          <t>1108218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2009222</t>
+          <t>2093701</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2009222</t>
+          <t>2093701</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2009222</t>
+          <t>2093701</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25203</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51393</t>
+          <t>55553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>143493</t>
+          <t>155081</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116137</t>
+          <t>135676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>172756</t>
+          <t>179204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153163</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211769</t>
+          <t>222488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3410675</t>
+          <t>3479108</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3396675</t>
+          <t>3463463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3422865</t>
+          <t>3489747</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3504855</t>
+          <t>3562037</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3475592</t>
+          <t>3537914</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3532211</t>
+          <t>3581442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6915529</t>
+          <t>7041145</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6884647</t>
+          <t>7013646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6943253</t>
+          <t>7067934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3448068</t>
+          <t>3519016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3648348</t>
+          <t>3717118</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7096416</t>
+          <t>7236134</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
